--- a/satisfaction_surveys/003_sewing_pattern_feedback_survey--satisfaction_surveys.xlsx
+++ b/satisfaction_surveys/003_sewing_pattern_feedback_survey--satisfaction_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -757,8 +757,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -786,12 +786,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'knit'}</t>
+          <t>knit</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Knit'}</t>
+          <t>Knit</t>
         </is>
       </c>
     </row>
@@ -803,12 +803,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'print'}</t>
+          <t>print</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Print'}</t>
+          <t>Print</t>
         </is>
       </c>
     </row>
@@ -820,12 +820,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -837,12 +837,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'a-line'}</t>
+          <t>a-line</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'A-line'}</t>
+          <t>A-line</t>
         </is>
       </c>
     </row>
@@ -854,12 +854,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'a-line_(with_curves)'}</t>
+          <t>a-line_(with_curves)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'A-line (with curves)'}</t>
+          <t>A-line (with curves)</t>
         </is>
       </c>
     </row>
@@ -871,12 +871,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'a-line_with_curves_and_pockets'}</t>
+          <t>a-line_with_curves_and_pockets</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'A-line with curves and pockets'}</t>
+          <t>A-line with curves and pockets</t>
         </is>
       </c>
     </row>
@@ -888,12 +888,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'b-line'}</t>
+          <t>b-line</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'B-line'}</t>
+          <t>B-line</t>
         </is>
       </c>
     </row>
@@ -905,12 +905,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'b-line_with_curves'}</t>
+          <t>b-line_with_curves</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'B-line with curves'}</t>
+          <t>B-line with curves</t>
         </is>
       </c>
     </row>
@@ -922,12 +922,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_6,_'name':_'b-line_with_pockets'}</t>
+          <t>b-line_with_pockets</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 6, 'name': 'B-line with pockets'}</t>
+          <t>B-line with pockets</t>
         </is>
       </c>
     </row>
@@ -939,12 +939,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_7,_'name':_'b-line_with_curves_and_pockets'}</t>
+          <t>b-line_with_curves_and_pockets</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 7, 'name': 'B-line with curves and pockets'}</t>
+          <t>B-line with curves and pockets</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_8,_'name':_'c-line'}</t>
+          <t>c-line</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 8, 'name': 'C-line'}</t>
+          <t>C-line</t>
         </is>
       </c>
     </row>
@@ -973,12 +973,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_9,_'name':_'c-line_with_curves'}</t>
+          <t>c-line_with_curves</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 9, 'name': 'C-line with curves'}</t>
+          <t>C-line with curves</t>
         </is>
       </c>
     </row>
@@ -990,12 +990,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_10,_'name':_'c-line_with_pockets'}</t>
+          <t>c-line_with_pockets</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 10, 'name': 'C-line with pockets'}</t>
+          <t>C-line with pockets</t>
         </is>
       </c>
     </row>
@@ -1007,12 +1007,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'xs-s'}</t>
+          <t>xs-s</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'XS-S'}</t>
+          <t>XS-S</t>
         </is>
       </c>
     </row>
@@ -1024,12 +1024,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'s'}</t>
+          <t>s</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'S'}</t>
+          <t>S</t>
         </is>
       </c>
     </row>
@@ -1041,12 +1041,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'m'}</t>
+          <t>m</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'M'}</t>
+          <t>M</t>
         </is>
       </c>
     </row>
@@ -1058,12 +1058,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'l'}</t>
+          <t>l</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'L'}</t>
+          <t>L</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'xl'}</t>
+          <t>xl</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'XL'}</t>
+          <t>XL</t>
         </is>
       </c>
     </row>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_6,_'name':_'xxl'}</t>
+          <t>xxl</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 6, 'name': 'XXL'}</t>
+          <t>XXL</t>
         </is>
       </c>
     </row>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_7,_'name':_'custom'}</t>
+          <t>custom</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 7, 'name': 'Custom'}</t>
+          <t>Custom</t>
         </is>
       </c>
     </row>
@@ -1126,12 +1126,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'knit'}</t>
+          <t>knit</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Knit'}</t>
+          <t>Knit</t>
         </is>
       </c>
     </row>
@@ -1143,12 +1143,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'crochet'}</t>
+          <t>crochet</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Crochet'}</t>
+          <t>Crochet</t>
         </is>
       </c>
     </row>
@@ -1160,12 +1160,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'print'}</t>
+          <t>print</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Print'}</t>
+          <t>Print</t>
         </is>
       </c>
     </row>
